--- a/docs/PTC_Mask_Transfer_PLC_HMI_Design.xlsx
+++ b/docs/PTC_Mask_Transfer_PLC_HMI_Design.xlsx
@@ -23,6 +23,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_來源與版本" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_總覽" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_CODEX審查封口" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_Fault_Output_Matrix" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_Timeout_參數標準" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_HMI權限與互鎖" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -109,7 +112,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -167,11 +170,43 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -218,6 +253,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -1172,31 +1209,11 @@
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>進入條件</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>主要動作</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>完成條件</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>異常/Timeout</t>
-        </is>
-      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
       <c r="G1" s="14" t="inlineStr">
         <is>
           <t>M/D/備註</t>
@@ -2078,31 +2095,11 @@
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>進入條件</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>主要動作</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>完成條件</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>異常/Timeout</t>
-        </is>
-      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
       <c r="G1" s="14" t="inlineStr">
         <is>
           <t>M/D/備註</t>
@@ -2729,31 +2726,11 @@
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>進入條件</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>主要動作</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>完成條件</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>異常/Timeout</t>
-        </is>
-      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
       <c r="G1" s="14" t="inlineStr">
         <is>
           <t>備註</t>
@@ -3224,31 +3201,11 @@
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>進入條件</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>主要動作</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>完成條件</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>異常/Timeout</t>
-        </is>
-      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
       <c r="G1" s="14" t="inlineStr">
         <is>
           <t>備註</t>
@@ -3537,31 +3494,11 @@
           <t>畫面/功能</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>HMI操作點</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>PLC對應</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>允許條件</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>禁止條件</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>設計說明</t>
-        </is>
-      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
@@ -4126,31 +4063,11 @@
           <t>代碼</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>中文名稱</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>等級</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>觸發條件</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>PLC處理</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>HMI排除方式</t>
-        </is>
-      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
@@ -4710,7 +4627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4725,21 +4642,11 @@
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>原因</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Release前必做</t>
-        </is>
-      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="20" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="21" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
@@ -5062,13 +4969,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="86" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5101,46 +5008,46 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS_TO_CODING</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>本檔作為力成光罩傳送機 PLC/HMI 程式設計標準版。內容依審查表整合，不採追加式零散補充。</t>
+          <t>本版依 20260825 最新驗證建議表整理，作為 PLC/HMI Coding 標準版。</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>可進入 PLC/HMI Coding 與單機測試。</t>
+          <t>不得再沿用舊版衝突M/D/S定義。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>整機 Release</t>
+          <t>主要修正</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>文件可作 Coding 依據，但不是現場整機驗收通過。</t>
+          <t>補 Formal I/O Master、Fault Output Matrix、Timeout參數、HMI權限/手動互鎖、Axis Ready/Alarm來源。</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>仍需 SR-2000W、Z高度、Tolerance、安全停止、真空/煞車策略實測。</t>
+          <t>這些是GX Works3 Coding前必備。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>2軸 X橫移/X升降</t>
+          <t>2軸流程</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
@@ -5150,19 +5057,19 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>S100/S150/S190 與 S200 子流程已可銜接 MAIN 與 FX5-40SSC-S。</t>
+          <t>X橫移/X升降正反向、自動、初始化、異常出口已可Coding。</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Coding 時使用 M1226/M1227/M1228 作子流程 Busy/Done/Alarm。</t>
+          <t>仍需現場確認D441x/D443x實際位置。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Z升降 + Barcode</t>
+          <t>Z升降+Barcode</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -5172,12 +5079,12 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>S300 補入檢查站氣缸定位、光罩在席、Z平台位、氣缸縮回、Barcode高度、掃碼比對。</t>
+          <t>S300保留檢查站氣缸定位、在席、Z平台位、氣缸縮回、Barcode高度、掃碼比對。</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>SR-2000W 字串格式、Byte order、Timeout 需實機確認。</t>
+          <t>SR-2000W通訊格式與Timeout需實測。</t>
         </is>
       </c>
     </row>
@@ -5194,12 +5101,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>S400 僅允許工程/手動調機使用，禁止自動流程使用。</t>
+          <t>僅手動/工程調機，禁止自動流程引用D6412旋轉。</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>入口條件為 M6010 工程/手動 + M6400 Z旋轉手動調機。</t>
+          <t>S400入口需M6010+M6400+X0000。</t>
         </is>
       </c>
     </row>
@@ -5216,56 +5123,34 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>補入自動、手動調機、Barcode、Alarm、Reset、I/O監看、Recipe/Teach。</t>
+          <t>補Machine Ready、Material Flow、Manual/JOG、Teach、Timeout、Reset、Alarm detail。</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>M6013/M6014 對應軸2 JOG-/JOG+，不可再寫到 M4330。</t>
+          <t>Auto Busy中禁止手動與人工料態套用。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>M/D位址標準</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>M0~M6999 / D0~D6999 分類整理；M4330 定義已固定為軸2真空確認位命令。</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>D4100/D4300/D4504/D4704 為 Tolerance，工程值待實測。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>成熟度</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>可交付 PLC/HMI 程式設計；整機 Release 前仍須現場測試封口。</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>不得把 PASS_TO_CODING 解讀為量產驗收通過。</t>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>整機Release</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>這是設計文件通過，不是現場Release通過。</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>FAT/SAT前需完成SR-2000W、Z高度、Tolerance、Safety OFF、Air OFF、真空/煞車策略實測。</t>
         </is>
       </c>
     </row>
@@ -6040,7 +5925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6310,22 +6195,22 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>HMI Reset混用</t>
+          <t>Formal I/O Master不足</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Safety/Alarm/Servo Reset混在一起。</t>
+          <t>缺Normal State/Active Level/NPN-PNP/COM/Terminal/Cable/Ref。</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>分M6040/M6041/M6042，Y0000只作安全繼電器瞬時復歸。</t>
+          <t>02_XY點位表重整為正式I/O Master欄位。</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
@@ -6335,29 +6220,29 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>14_HMI畫面標準</t>
+          <t>02_XY點位表</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>儲存盒/上機盒光罩存在無DI</t>
+          <t>Fault Output Matrix不足</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>曾留TBD-DI。</t>
+          <t>異常時不可一律關閉所有輸出。</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>依使用者確認改為由真空OK與流程狀態推導；只有檢查站X0026為實體DI。</t>
+          <t>新增18_Fault_Output_Matrix，定義真空/煞車/MC/輸出策略。</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
@@ -6367,39 +6252,1441 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>02_XY點位表</t>
+          <t>18_Fault_Output_Matrix</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Timeout未參數化</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Move/Grip/Vacuum/Release/Z timeout缺統一D參數。</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>新增D6020~D6028與19_Timeout_參數標準。</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>08_D資料參數 / 19_Timeout_參數標準</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>HMI Manual/JOG互鎖不足</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy時可能誤操作手動。</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>新增M6200/M6201與20_HMI權限與互鎖。</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>03_M共用_HMI_Barcode / 20_HMI權限與互鎖</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>HMI Reset需拆分</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Alarm/Servo/Safety Reset需分離。</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>M6040/M6041/M6042已列入，Y0000只做安全復歸瞬時輸出。</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>03_M共用_HMI_Barcode / 20_HMI權限與互鎖</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Auto Stop與Abort需拆分</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>M6004語意不足。</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>M6004=Normal Stop，M6008=Abort中止。</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>03_M共用_HMI_Barcode / 20_HMI權限與互鎖</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Material State人工修正需權限</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>D6101可被誤改。</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>D6101需Engineer、M6030 Apply、M6031 Confirm、Auto Busy禁止。</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>08_D資料參數 / 20_HMI權限與互鎖</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>等級</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>X/Y輸出策略</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>真空策略</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>煞車策略</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>伺服/MC策略</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>恢復方式</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>K101 安全繼電器NG</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>停止新動作；安全相關輸出依硬體斷電</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>若光罩在手臂，依現場策略保持真空或安全洩放</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>垂直軸煞車落下</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>切斷伺服MC或STO依安全設計</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>安全復歸M6042後重新初始化</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>不得由PLC取代安全迴路。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>K102 氣壓不足</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>停止所有氣缸新命令</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>預設保持真空；若氣源不足無法保持需現場評估</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>煞車保持</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>停止軸動作，不一定立即切MC</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>恢復氣壓後M6040再初始化</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>避免一律OFF造成掉片。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>K150 X橫移定位異常</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>停止X橫移命令</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>保持目前真空</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>煞車依軸別</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Axis1停止/Servo保持</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>排除後回S190初始化</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>K160 X升降定位異常</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>停止X升降命令</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>保持目前真空</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>X升降煞車依停止順序落下</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Axis2停止/Servo保持或切MC依現場</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>排除後回S190/S290初始化</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>K171 X/Z交握Timeout</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>停止X進檢查區與Z新動作</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>保持目前真空</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>煞車保持</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>X/Z伺服停止但不亂切</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>確認Z安全位後復歸</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>K180 氣缸到位異常</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>停止相關電磁閥新命令</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>保持或依步序處理</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>煞車保持</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>伺服不新增移動</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>查氣缸/磁簧/電磁閥</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>K200 真空建立失敗</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>停機</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>停止上升/橫移</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>真空ON保持並報警，禁止放片</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>煞車保持</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>伺服保持</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>查吸盤/漏氣後重試或人工排除</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>K201 破真空失敗</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>停機/警告</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>停止放夾下一步</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>破真空ON或要求人工確認</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>煞車保持</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>伺服保持</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>查破真空閥</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>K210 靜電消除器檢查</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>警告</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>不停止自動，HMI提示</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>不影響</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>不影響</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>不影響</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>維護後清除</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>K211 靜電消除器異常</t>
+        </is>
+      </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>整機Release誤判</t>
+          <t>停機</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>文件通過不等於現場驗收。</t>
+          <t>禁止下一片自動</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Release Gate明確標示PASS_TO_CODING，整機Release HOLD。</t>
+          <t>保持目前真空</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>煞車保持</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>16_驗收_Release_Gate</t>
+          <t>流程停在安全點</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>排除後復歸</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>K230 FFU/排風異常</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>警告/停機待定</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>依潔淨需求禁止啟動或停在安全點</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>保持目前真空</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>煞車保持</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>不一定切MC</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>查FFU/濾網/壓差</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>依業主標準決定等級。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="68" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Timeout項目</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>D位址</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>預設建議</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>觸發範圍</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>對應警報</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>HMI權限</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>設計說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>X橫移定位</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>D6020/軸別覆寫</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>工程待定</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>S110/S119/S140/S160/S162/S170/S193</t>
+        </is>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
+        <is>
+          <t>K150</t>
+        </is>
+      </c>
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>依行程距離與速度計算，不寫死K常數。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>X升降定位</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>D6020/軸別覆寫</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>工程待定</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>S210~S290</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>K160</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>垂直軸需含煞車釋放時間。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>夾爪開關</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>D6022</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>工程待定</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>S211/S222等</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>K180</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>依磁簧回授。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>真空建立</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>D6024</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>工程待定</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>取片真空ON後</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>K200</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>X0027/X0030/X0031未ON。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>破真空</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>D6026</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>工程待定</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>放片破真空後</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>K201</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>真空OK未OFF或延時未完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>X/Z交握</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>D6028</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>工程待定</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>等待M6102/M6103</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>K171</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>防止stale Done。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Barcode讀取</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>D6422</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>工程待定</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>S306/S307</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>K181/K182</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>依SR-2000W實測通訊時間。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>功能</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>必須條件</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>禁止條件</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>PLC點位/資料</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>自動正向/反向啟動</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>Safety OK、Air OK、Init OK、Ready、Z Safe、Material一致</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy、Alarm、Manual Mode</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>M6002/M6003</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Auto Stop</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr"/>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>M6004</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Abort中止</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>限制</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr"/>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>M6008</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Alarm Reset</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>異常條件解除</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Safety未復歸</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>M6040</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Servo Reset</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>軸停止、Safety OK</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>軸Busy</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>M6041</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Safety Reset</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>EMO釋放、門鎖成立</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>安全條件未成立</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>M6042/Y0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Manual/JOG</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>M6010、M6200、低速、軸停止</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy、Safety NG</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>M6011~M6018/M6200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>氣缸/真空單動</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>手動模式、位置安全、二次確認</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy、Safety NG</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>Y0007~Y0022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>位置Teach</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>手動模式、軸停止、確認視窗</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>D441x/D451x/D471x</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Tolerance/Speed/Timeout</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>工程權限、上下限檢查</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>D4100/D4300/D602x</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>人工料態修正</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>允許</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>M6030 Apply、二次確認、Sensor一致檢查</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>D6101/M6030/M6031</t>
         </is>
       </c>
     </row>
@@ -6414,80 +7701,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="66" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>02_XY點位表</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
-      <c r="G1" s="14" t="n"/>
-      <c r="H1" s="14" t="n"/>
-      <c r="I1" s="14" t="n"/>
+          <t>位址</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Normal State</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Active Level</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>NPN/PNP/接點</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>COM</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Cable/Drawing Ref</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>設計說明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>位址</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>中文名稱</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>分類</t>
-        </is>
-      </c>
-      <c r="F2" s="15" t="inlineStr">
-        <is>
-          <t>設計注意</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="n"/>
-      <c r="H2" s="16" t="n"/>
-      <c r="I2" s="16" t="n"/>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>X0000</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>安全繼電器OK</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>ON=安全成立</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>24V ON</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0000</t>
+        </is>
+      </c>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>安全迴路總回授，PLC只監看。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>X0000</t>
+          <t>X0001</t>
         </is>
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>安全繼電器OK</t>
+          <t>氣壓源OK</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
@@ -6497,7 +7838,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>ON=安全成立</t>
+          <t>ON=氣壓正常</t>
         </is>
       </c>
       <c r="E3" s="16" t="inlineStr">
@@ -6507,34 +7848,39 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
           <t>DI-COM0</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0000</t>
-        </is>
-      </c>
       <c r="H3" s="16" t="inlineStr">
         <is>
+          <t>TB-X0001</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>安全迴路總回授，PLC只監看，不取代安全繼電器。</t>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>氣壓不足停機。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>X0001</t>
+          <t>X0002</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>氣壓源OK</t>
+          <t>X軸橫移_負極限</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -6544,7 +7890,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>ON=氣壓正常</t>
+          <t>ON=極限觸發</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
@@ -6554,734 +7900,1079 @@
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
           <t>DI-COM0</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0001</t>
-        </is>
-      </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
+          <t>TB-X0002</t>
+        </is>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>氣壓不足停機。</t>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>軸卡RLS/PLC監看。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>X0002</t>
+          <t>X0003</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>X軸橫移_負極限</t>
+          <t>X軸橫移_原點</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>X traverse negative limit</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=原點</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>軸1</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 RLS</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="n"/>
-      <c r="I5" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0003</t>
+        </is>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>DOG/原點。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>X0003</t>
+          <t>X0004</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>X軸橫移_原點</t>
+          <t>X軸橫移_正極限</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>X traverse DOG/home</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=極限觸發</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>軸1</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 DOG</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="n"/>
-      <c r="H6" s="16" t="n"/>
-      <c r="I6" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0004</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>軸卡FLS/PLC監看。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>X0004</t>
+          <t>X0005</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>X軸橫移_正極限</t>
+          <t>X軸升降_負極限</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>X traverse positive limit</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=極限觸發</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>軸1</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 FLS</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0005</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>軸卡RLS/PLC監看。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>X0005</t>
+          <t>X0006</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>X軸升降_負極限</t>
+          <t>X軸升降_原點</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>X lift negative limit</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=原點</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>軸2</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 RLS</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0006</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>DOG/原點。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>X0006</t>
+          <t>X0007</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>X軸升降_原點</t>
+          <t>X軸升降_正極限</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>X lift DOG/home</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=極限觸發</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>軸2</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 DOG</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="n"/>
-      <c r="H9" s="16" t="n"/>
-      <c r="I9" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0007</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>軸卡FLS/PLC監看。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>X0007</t>
+          <t>X0010</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>X軸升降_正極限</t>
+          <t>Z軸升降_負極限</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>X lift positive limit</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=極限觸發</t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>軸2</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 FLS</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="n"/>
-      <c r="H10" s="16" t="n"/>
-      <c r="I10" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0010</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>Z升降限位。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>X0010</t>
+          <t>X0011</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Z軸升降_負極限</t>
+          <t>Z軸升降_原點</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Z lift negative limit</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=原點</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>軸3</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 RLS</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-      <c r="I11" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0011</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Z升降原點。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>X0011</t>
+          <t>X0012</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Z軸升降_原點</t>
+          <t>Z軸升降_正極限</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Z lift DOG/home</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=極限觸發</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>軸3</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 DOG</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0012</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>Z升降限位。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>X0012</t>
+          <t>X0013</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Z軸升降_正極限</t>
+          <t>Z軸旋轉_原點</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Z lift positive limit</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=原點</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>軸3</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>接軸卡 FLS</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM0</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0013</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>Z旋轉原點。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>X0013</t>
+          <t>X0014</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Z軸旋轉_原點</t>
+          <t>X軸氣缸左右夾爪_開</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Z rotation DOG/home</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=開到位</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>軸4</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>旋轉軸只需原點</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0014</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>夾爪開確認。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>X0014</t>
+          <t>X0015</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>X軸氣缸左右夾爪_開</t>
+          <t>X軸氣缸左右夾爪_關</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>X gripper open</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=關到位</t>
         </is>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>磁簧</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="16" t="n"/>
-      <c r="I15" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0015</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>夾爪關確認。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>X0015</t>
+          <t>X0016</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>X軸氣缸左右夾爪_關</t>
+          <t>檢查站氣缸左右定位_開</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>X gripper close</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=開到位</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>磁簧</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-      <c r="I16" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0016</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>檢查站定位。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>X0016</t>
+          <t>X0017</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>檢查站氣缸左右定位_開</t>
+          <t>檢查站氣缸左右定位_關</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Inspection side cylinder open</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=關到位</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>磁簧</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="16" t="n"/>
-      <c r="I17" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0017</t>
+        </is>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>檢查站定位。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>X0017</t>
+          <t>X0020</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>檢查站氣缸左右定位_關</t>
+          <t>檢查站氣缸前後定位_開</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Inspection side cylinder close</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=開到位</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>磁簧</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="16" t="n"/>
-      <c r="I18" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0020</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>檢查站定位。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>X0020</t>
+          <t>X0021</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>檢查站氣缸前後定位_開</t>
+          <t>檢查站氣缸前後定位_關</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>Inspection front/back cylinder open</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=關到位</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>磁簧</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0021</t>
+        </is>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>檢查站定位。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>X0021</t>
+          <t>X0022</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>檢查站氣缸前後定位_關</t>
+          <t>儲存盒在席定位</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Inspection front/back cylinder close</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=盒在席</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>磁簧</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0022</t>
+        </is>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>盒在席，不等於盒內光罩存在。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>X0022</t>
+          <t>X0023</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>儲存盒在席定位</t>
+          <t>儲存盒開蓋定位</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>Storage box present</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=開蓋到位</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>盒位</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>正式實體DI</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="16" t="n"/>
-      <c r="I21" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0023</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>儲存盒開蓋。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>X0023</t>
+          <t>X0024</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>儲存盒開蓋定位</t>
+          <t>上機盒在席定位</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Storage box lid open</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=盒在席</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>盒位</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>正式實體DI</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0024</t>
+        </is>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>盒在席，不等於盒內光罩存在。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>X0024</t>
+          <t>X0025</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>上機盒在席定位</t>
+          <t>上機盒開蓋定位</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>Tool box present</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=開蓋到位</t>
         </is>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>盒位</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>正式實體DI</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0025</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>上機盒開蓋。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>X0025</t>
+          <t>X0026</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>上機盒開蓋定位</t>
+          <t>光罩在席定位</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Tool box lid open</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=檢查站有光罩</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>盒位</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>正式實體DI</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="16" t="n"/>
-      <c r="I24" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM1</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0026</t>
+        </is>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>檢查站光罩存在實體輸入。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>X0026</t>
+          <t>X0027</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>光罩在席定位</t>
+          <t>X軸手臂真空OK</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -7291,7 +8982,7 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>ON=檢查站有光罩</t>
+          <t>ON=吸附成立</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
@@ -7301,34 +8992,39 @@
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
           <t>DI-COM1</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0026</t>
-        </is>
-      </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
+          <t>TB-X0027</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>檢查站光罩存在實體輸入。</t>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>手臂吸附確認。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>X0027</t>
+          <t>X0030</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>X軸手臂真空OK</t>
+          <t>儲存盒真空OK</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
@@ -7338,7 +9034,7 @@
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>ON=吸附成立</t>
+          <t>ON=真空成立</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -7348,34 +9044,39 @@
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
           <t>DI-COM1</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0027</t>
-        </is>
-      </c>
       <c r="H26" s="16" t="inlineStr">
         <is>
+          <t>TB-X0030</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>儲存盒/上機盒無獨立光罩Sensor時，用真空OK與流程狀態推導。</t>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>儲存盒光罩存在由真空OK+流程狀態推導。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>X0030</t>
+          <t>X0031</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>儲存盒真空OK</t>
+          <t>上機盒真空OK</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -7385,7 +9086,7 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>ON=吸附/真空成立</t>
+          <t>ON=真空成立</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
@@ -7395,34 +9096,39 @@
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
           <t>DI-COM1</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>TB-X0030</t>
-        </is>
-      </c>
       <c r="H27" s="16" t="inlineStr">
         <is>
+          <t>TB-X0031</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>作為儲存盒取放狀態推導，不另設儲存盒光罩存在DI。</t>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>上機盒光罩存在由真空OK+流程狀態推導。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>X0031</t>
+          <t>X0032</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>上機盒真空OK</t>
+          <t>靜電消除器檢查</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -7432,7 +9138,7 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>ON=吸附/真空成立</t>
+          <t>ON=Check</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
@@ -7442,384 +9148,551 @@
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>DI-COM1</t>
+          <t>NPN輸入/漏型PLC</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>TB-X0031</t>
+          <t>DI-COM2</t>
         </is>
       </c>
       <c r="H28" s="16" t="inlineStr">
         <is>
+          <t>TB-X0032</t>
+        </is>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>作為上機盒取放狀態推導，不另設上機盒光罩存在DI。</t>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>警告。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>X0032</t>
+          <t>X0033</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>靜電消除器檢查</t>
+          <t>靜電消除器異常</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>Ionizer check</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=Alarm</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>靜電</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>警告類</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM2</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0033</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>停機。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>X0033</t>
+          <t>X0034</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>靜電消除器異常</t>
+          <t>排風壓差低</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>Ionizer alarm</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=Low</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>靜電</t>
+          <t>乾接點/24V回路</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>停機或禁止自動，依客戶規範</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
+          <t>DI-COM2</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0034</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>Dwyer壓差表警報回授。</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>X0034</t>
+          <t>X0035</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>排風壓差低</t>
+          <t>排風壓差高</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>Exhaust pressure low</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=High</t>
         </is>
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>排氣</t>
+          <t>乾接點/24V回路</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>警告/禁止啟動</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
+          <t>DI-COM2</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0035</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>Dwyer壓差表警報回授。</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>X0035</t>
+          <t>X0036</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>排風壓差高</t>
+          <t>FFU運轉中</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Exhaust pressure high</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=Run</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>排氣</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>警告/停機依規範</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM2</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0036</t>
+        </is>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>若FFU有Run接點才接。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>X0036</t>
+          <t>X0037</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>FFU運轉中</t>
+          <t>FFU異常</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>FFU running</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=Alarm</t>
         </is>
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>FFU</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>狀態監看</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>DI-COM2</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0037</t>
+        </is>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>若FFU有Alarm接點才接。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>X0037</t>
+          <t>X0040</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>FFU異常</t>
+          <t>EMO1</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>FFU alarm</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=EMO正常/輔助接點</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>FFU</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>警告/停機依規範</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="n"/>
-      <c r="H34" s="16" t="n"/>
-      <c r="I34" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>擴充DI-COM</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0040</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>PLC監看用，不取代安全迴路。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>X0040</t>
+          <t>X0041</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>EMO1輔助監看</t>
+          <t>EMO2</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>E-stop 1 monitor</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=EMO正常/輔助接點</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>安全監看</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>安全回路主接點仍進安全繼電器</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="16" t="n"/>
-      <c r="I35" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>擴充DI-COM</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0041</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>PLC監看用。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>X0041</t>
+          <t>X0042</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>EMO2輔助監看</t>
+          <t>EMO3</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>E-stop 2 monitor</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=EMO正常/輔助接點</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>安全監看</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>輔助接點給PLC顯示</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>擴充DI-COM</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0042</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>PLC監看用。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>X0042</t>
+          <t>X0043</t>
         </is>
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>EMO3輔助監看</t>
+          <t>EMO4</t>
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>E-stop 3 monitor</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>ON=EMO正常/輔助接點</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
-          <t>安全監看</t>
+          <t>24V ON</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>輔助接點給PLC顯示</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="16" t="n"/>
+          <t>NPN輸入/漏型PLC</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>擴充DI-COM</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>TB-X0043</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>PLC監看用。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>X0043</t>
+          <t>Y0000</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>EMO4輔助監看</t>
+          <t>安全繼電器復歸</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>E-stop 4 monitor</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>瞬時ON</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>安全監看</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
-          <t>輔助接點給PLC顯示</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="16" t="n"/>
+          <t>晶體輸出</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM0</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0000</t>
+        </is>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>Safety Reset Request後瞬時輸出。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Y0000</t>
+          <t>Y0001</t>
         </is>
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>安全繼電器復歸</t>
+          <t>X軸升降煞車</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
@@ -7829,7 +9702,7 @@
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>瞬時ON</t>
+          <t>ON=釋放煞車</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -7839,34 +9712,39 @@
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
+          <t>晶體輸出+Relay建議</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
           <t>DO-COM0</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0000</t>
-        </is>
-      </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
+          <t>TB-Y0001</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>HMI Safety Reset Request 後輸出瞬時復歸，不得長ON。</t>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>Z/垂直軸需與伺服Ready互鎖。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Y0001</t>
+          <t>Y0002</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>X軸升降煞車</t>
+          <t>Z軸升降煞車</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
@@ -7886,69 +9764,91 @@
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
+          <t>晶體輸出+Relay建議</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
           <t>DO-COM0</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0001</t>
-        </is>
-      </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
+          <t>TB-Y0002</t>
+        </is>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>需與伺服ON、軸Ready、停止策略互鎖。</t>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>Z升降垂直軸。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Y0002</t>
+          <t>Y0003</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Z軸升降煞車(Relay)</t>
+          <t>X軸橫移伺服電源</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>Z lift brake</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=MC吸合</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>煞車</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>伺服ON/動作時釋放，停止時落煞</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="16" t="n"/>
-      <c r="I41" s="16" t="n"/>
+          <t>晶體輸出+Relay/接觸器</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM0</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0003</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>伺服電源接觸器。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Y0003</t>
+          <t>Y0004</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>X軸橫移伺服電源</t>
+          <t>X軸升降伺服電源</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
@@ -7968,34 +9868,39 @@
       </c>
       <c r="F42" s="16" t="inlineStr">
         <is>
+          <t>晶體輸出+Relay/接觸器</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
           <t>DO-COM0</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0003</t>
-        </is>
-      </c>
       <c r="H42" s="16" t="inlineStr">
         <is>
+          <t>TB-Y0004</t>
+        </is>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>驅動接觸器Relay或接觸器線圈，依線圈電流決定。</t>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>伺服電源接觸器。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Y0004</t>
+          <t>Y0005</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>X軸升降伺服電源</t>
+          <t>Z軸升降伺服電源</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
@@ -8015,527 +9920,779 @@
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
+          <t>晶體輸出+Relay/接觸器</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
           <t>DO-COM0</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0004</t>
-        </is>
-      </c>
       <c r="H43" s="16" t="inlineStr">
         <is>
+          <t>TB-Y0005</t>
+        </is>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>驅動接觸器Relay或接觸器線圈，依線圈電流決定。</t>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>伺服電源接觸器。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Y0005</t>
+          <t>Y0006</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Z軸升降伺服電源(Relay)</t>
+          <t>Z軸旋轉伺服電源</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>Z lift servo power</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=MC吸合</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>伺服電源</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>控制MC/Relay線圈</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="16" t="n"/>
-      <c r="I44" s="16" t="n"/>
+          <t>晶體輸出+Relay/接觸器</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM0</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0006</t>
+        </is>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>伺服電源接觸器。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Y0006</t>
+          <t>Y0007</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>Z軸旋轉伺服電源(Relay)</t>
+          <t>X軸左右氣缸電磁閥_開</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>Z rotation servo power</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=開</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>伺服電源</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>控制MC/Relay線圈</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="16" t="n"/>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0007</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>依電磁閥線圈電流確認。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Y0007</t>
+          <t>Y0010</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>X軸左右氣缸電磁閥_開</t>
+          <t>X軸左右氣缸電磁閥_關</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>X gripper valve open</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=關</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>依電磁閥線圈電流確認是否直驅</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="16" t="n"/>
-      <c r="I46" s="16" t="n"/>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0010</t>
+        </is>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Y0010</t>
+          <t>Y0011</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>X軸左右氣缸電磁閥_關</t>
+          <t>檢查站左右電磁閥_開</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>X gripper valve close</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=開</t>
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>依電磁閥線圈電流確認是否直驅</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="16" t="n"/>
-      <c r="I47" s="16" t="n"/>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0011</t>
+        </is>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Y0011</t>
+          <t>Y0012</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>檢查站左右電磁閥_開</t>
+          <t>檢查站左右電磁閥_關</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>Inspection side valve open</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=關</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
-        </is>
-      </c>
-      <c r="F48" s="16" t="str"/>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="16" t="n"/>
-      <c r="I48" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0012</t>
+        </is>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Y0012</t>
+          <t>Y0013</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>檢查站左右電磁閥_關</t>
+          <t>檢查站前後電磁閥_開</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>Inspection side valve close</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=開</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="str"/>
-      <c r="G49" s="16" t="n"/>
-      <c r="H49" s="16" t="n"/>
-      <c r="I49" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0013</t>
+        </is>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Y0013</t>
+          <t>Y0014</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>檢查站前後電磁閥_開</t>
+          <t>檢查站前後電磁閥_關</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>Inspection front/back valve open</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=關</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="str"/>
-      <c r="G50" s="16" t="n"/>
-      <c r="H50" s="16" t="n"/>
-      <c r="I50" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0014</t>
+        </is>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Y0014</t>
+          <t>Y0015</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>檢查站前後電磁閥_關</t>
+          <t>X軸手臂真空ON</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>Inspection front/back valve close</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=真空</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>氣缸</t>
-        </is>
-      </c>
-      <c r="F51" s="16" t="str"/>
-      <c r="G51" s="16" t="n"/>
-      <c r="H51" s="16" t="n"/>
-      <c r="I51" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0015</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>異常時是否保持依Fault Matrix。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Y0015</t>
+          <t>Y0016</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>X軸手臂真空ON(Relay)</t>
+          <t>X軸手臂破真空</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>X arm vacuum ON</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=破真空</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>真空</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
         <is>
-          <t>取片前ON，放片前OFF/破真空</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="n"/>
-      <c r="H52" s="16" t="n"/>
-      <c r="I52" s="16" t="n"/>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0016</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Y0016</t>
+          <t>Y0017</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>X軸手臂破真空(Relay)</t>
+          <t>儲存盒真空ON</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>X arm vacuum release</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=真空</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>真空</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>放片時短暫作動</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="n"/>
-      <c r="H53" s="16" t="n"/>
-      <c r="I53" s="16" t="n"/>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0017</t>
+        </is>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Y0017</t>
+          <t>Y0020</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>儲存盒真空ON(Relay)</t>
+          <t>儲存盒破真空</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>Storage vacuum ON</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=破真空</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>真空</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="str"/>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="16" t="n"/>
-      <c r="I54" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0020</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Y0020</t>
+          <t>Y0021</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>儲存盒破真空(Relay)</t>
+          <t>上機盒真空ON</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>Storage vacuum release</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=真空</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>真空</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="str"/>
-      <c r="G55" s="16" t="n"/>
-      <c r="H55" s="16" t="n"/>
-      <c r="I55" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0021</t>
+        </is>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Y0021</t>
+          <t>Y0022</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>上機盒真空ON(Relay)</t>
+          <t>上機盒破真空</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>Tool box vacuum ON</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=破真空</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>真空</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="str"/>
-      <c r="G56" s="16" t="n"/>
-      <c r="H56" s="16" t="n"/>
-      <c r="I56" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅/需突波吸收</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM1</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0022</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Y0022</t>
+          <t>Y0023</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>上機盒破真空(Relay)</t>
+          <t>靜電消除器停止</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>Tool box vacuum release</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=停止/Disable</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>真空</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="str"/>
-      <c r="G57" s="16" t="n"/>
-      <c r="H57" s="16" t="n"/>
-      <c r="I57" s="16" t="n"/>
+          <t>24V OUT/乾接點依手冊</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>需確認DTY-ELK01</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM2</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0023</t>
+        </is>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>依實際接線確認Enable或Stop語意。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Y0023</t>
+          <t>Y0024</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>靜電消除器停止(Relay)</t>
+          <t>FFU電源ON</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>Ionizer stop</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=FFU供電</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>靜電</t>
+          <t>24V OUT</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>Enable/Stop 依DTY-ELK01接點邏輯現場確認</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="n"/>
-      <c r="H58" s="16" t="n"/>
-      <c r="I58" s="16" t="n"/>
+          <t>驅動接觸器</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM2</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0024</t>
+        </is>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>不可直接切AC負載。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Y0024</t>
+          <t>Y0034</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>FFU電源ON</t>
+          <t>三色燈-紅</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
@@ -8545,7 +10702,7 @@
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>ON=FFU供電</t>
+          <t>ON=紅燈</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr">
@@ -8555,169 +10712,171 @@
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
+          <t>晶體輸出可直驅</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
           <t>DO-COM2</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr">
-        <is>
-          <t>TB-Y0024</t>
-        </is>
-      </c>
       <c r="H59" s="16" t="inlineStr">
         <is>
+          <t>TB-Y0034</t>
+        </is>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>建議驅動接觸器線圈，不直接由PLC切AC負載。</t>
-        </is>
-      </c>
+      <c r="J59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Y0034</t>
+          <t>Y0035</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>三色燈-紅(Relay)</t>
+          <t>三色燈-黃</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>Tower light red</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=黃燈</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>警示</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="str"/>
-      <c r="G60" s="16" t="n"/>
-      <c r="H60" s="16" t="n"/>
-      <c r="I60" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM2</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0035</t>
+        </is>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Y0035</t>
+          <t>Y0036</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>三色燈-黃(Relay)</t>
+          <t>三色燈-綠</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>Tower light yellow</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=綠燈</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>警示</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="str"/>
-      <c r="G61" s="16" t="n"/>
-      <c r="H61" s="16" t="n"/>
-      <c r="I61" s="16" t="n"/>
+          <t>24V OUT</t>
+        </is>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>DO-COM2</t>
+        </is>
+      </c>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>TB-Y0036</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>待畫圖</t>
+        </is>
+      </c>
+      <c r="J61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Y0036</t>
+          <t>Y0037</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>三色燈-綠(Relay)</t>
+          <t>三色燈-蜂鳴器</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>Tower light green</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>ON=蜂鳴</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>警示</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="str"/>
-      <c r="G62" s="16" t="n"/>
-      <c r="H62" s="16" t="n"/>
-      <c r="I62" s="16" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>Y0037</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>三色燈-蜂鳴器</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>DO</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>ON=蜂鳴</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
           <t>24V OUT</t>
         </is>
       </c>
-      <c r="F63" s="16" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>晶體輸出可直驅</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>DO-COM2</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>TB-Y0037</t>
         </is>
       </c>
-      <c r="H63" s="16" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>待畫圖</t>
         </is>
       </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>若負載電流低於PLC單點/COM限制可直驅，需加突波抑制。</t>
-        </is>
-      </c>
+      <c r="J62" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8728,7 +10887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9731,27 +11890,27 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>自動停止</t>
+          <t>HMI Auto Stop</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>Auto stop</t>
+          <t>HMI auto stop</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>HMI自動</t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>只作自動停止</t>
+          <t>一般停止，跑到安全點停止。</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>不可作S400入口</t>
+          <t>Abort/E-stop需分開。</t>
         </is>
       </c>
     </row>
@@ -9915,25 +12074,29 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>Barcode掃描請求</t>
+          <t>Manual允許總旗標</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>Barcode scan request</t>
+          <t>Manual operation enable</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Barcode</t>
+          <t>手動調機</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>PLC要求SR-2000W讀碼</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="str"/>
+          <t>M6010 + Safety OK + Auto Busy OFF + Axis Stop。</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>JOG與單動輸出必須串此條件。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -9943,25 +12106,29 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>Barcode掃描中</t>
+          <t>JOG低速模式</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>Barcode scanning</t>
+          <t>JOG low speed mode</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Barcode</t>
+          <t>手動調機</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>讀碼中</t>
-        </is>
-      </c>
-      <c r="F43" s="16" t="str"/>
+          <t>手動JOG固定低速或限速。</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>維修模式速度需&lt;50mm/s時在此互鎖。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -9992,32 +12159,32 @@
       <c r="F44" s="16" t="str"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>M6203</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="18" t="inlineStr">
         <is>
           <t>Barcode NG</t>
         </is>
       </c>
-      <c r="C45" s="16" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>Barcode NG</t>
         </is>
       </c>
-      <c r="D45" s="16" t="inlineStr">
+      <c r="D45" s="18" t="inlineStr">
         <is>
           <t>Barcode</t>
         </is>
       </c>
-      <c r="E45" s="16" t="inlineStr">
+      <c r="E45" s="18" t="inlineStr">
         <is>
           <t>讀取失敗/比對失敗</t>
         </is>
       </c>
-      <c r="F45" s="16" t="inlineStr">
+      <c r="F45" s="18" t="inlineStr">
         <is>
           <t>走NG人工介入</t>
         </is>
@@ -10331,12 +12498,12 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>HMI反向啟動</t>
+          <t>HMI正向啟動</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>HMI reverse start</t>
+          <t>HMI forward start</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -10346,12 +12513,12 @@
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>上機盒到儲存盒啟動</t>
+          <t>Momentary，啟動M1102。</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>觸發M1103</t>
+          <t>依最新驗證表採M6002/M6003為正反啟動。</t>
         </is>
       </c>
     </row>
@@ -10363,25 +12530,29 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>HMI全部初始化</t>
+          <t>HMI反向啟動</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>HMI all initialize</t>
+          <t>HMI reverse start</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>HMI初始化</t>
+          <t>HMI自動</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>觸發M1001</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr"/>
+          <t>Momentary，啟動M1103。</t>
+        </is>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>Auto Busy中禁止。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -10525,17 +12696,17 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>HMI Reset</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>只清除可復歸警報與流程Alarm旗標。</t>
+          <t>只復歸可復歸警報。</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>不可直接復歸安全繼電器。</t>
+          <t>不自動重新啟動。</t>
         </is>
       </c>
     </row>
@@ -10547,7 +12718,7 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>HMI伺服異常復歸</t>
+          <t>HMI伺服復歸</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
@@ -10557,17 +12728,17 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>HMI Reset</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>觸發各軸伺服/軸卡錯誤復歸流程。</t>
+          <t>伺服/軸卡異常復歸。</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>需Safety OK與Servo Ready條件。</t>
+          <t>需軸停止。</t>
         </is>
       </c>
     </row>
@@ -10589,17 +12760,17 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>HMI</t>
+          <t>HMI Reset</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>驅動Y0000安全繼電器復歸瞬時輸出。</t>
+          <t>條件成立後瞬時Y0000。</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>需EMO釋放、門鎖成立。</t>
+          <t>安全繼電器復歸。</t>
         </is>
       </c>
     </row>
@@ -10717,17 +12888,49 @@
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>X/Z交握</t>
         </is>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
-          <t>X等待Z ACK或Done逾時SET。</t>
+          <t>等待ACK/Done逾時。</t>
         </is>
       </c>
       <c r="F68" s="16" t="inlineStr">
         <is>
           <t>Alarm K171。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>M6008</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>HMI Abort中止</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>HMI abort</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>HMI自動</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>中止目前流程，轉異常/安全停止出口。</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>不同於M6004 Normal Stop。</t>
         </is>
       </c>
     </row>
@@ -10745,625 +12948,682 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>04_M軸1_X橫移</t>
         </is>
       </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+      <c r="F1" s="14" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>位址</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>中文名稱</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>分類</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>用途</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>M4100</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_速度控制中標誌</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse speed control active</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F3" s="10" t="str"/>
+      <c r="F3" s="16" t="str"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>M4101</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_速度/位置切換鎖存</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse speed/position latch</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F4" s="10" t="str"/>
+      <c r="F4" s="16" t="str"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>M4102</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_指令到位標誌</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse command in position</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F5" s="10" t="str"/>
+      <c r="F5" s="16" t="str"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>M4103</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_原點回歸請求</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse home return request state</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F6" s="10" t="str"/>
+      <c r="F6" s="16" t="str"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>M4104</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_原點回歸完成</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse home return complete</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F7" s="10" t="str"/>
+      <c r="F7" s="16" t="str"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>M4109</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_軸報警檢測</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse axis alarm detected</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F8" s="10" t="str"/>
+      <c r="F8" s="16" t="str"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>M4112</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_M代碼ON</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse M-code ON</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F9" s="10" t="str"/>
+      <c r="F9" s="16" t="str"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>M4113</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_錯誤檢測</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse error detected</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F10" s="10" t="str"/>
+      <c r="F10" s="16" t="str"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>M4114</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_啟動完成</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse start complete</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F11" s="10" t="str"/>
+      <c r="F11" s="16" t="str"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>M4115</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_狀態_定位完成</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse positioning complete</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>軸卡狀態</t>
         </is>
       </c>
-      <c r="F12" s="10" t="str"/>
+      <c r="F12" s="16" t="str"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>M4116</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_初始化</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse initialize</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>MAIN初始化觸發</t>
         </is>
       </c>
-      <c r="F13" s="10" t="str"/>
+      <c r="F13" s="16" t="str"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>M4127</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_BUSY</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse BUSY</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>U1\G3150 bit狀態</t>
         </is>
       </c>
-      <c r="F14" s="10" t="str"/>
+      <c r="F14" s="16" t="str"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>M4131</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_JOG-</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse JOG-</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>HMI手動</t>
         </is>
       </c>
-      <c r="F15" s="10" t="str"/>
+      <c r="F15" s="16" t="str"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>M4132</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_JOG+</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse JOG+</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>HMI手動</t>
         </is>
       </c>
-      <c r="F16" s="10" t="str"/>
+      <c r="F16" s="16" t="str"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>M4120</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_儲存盒位命令</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse 儲存盒位 command</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>定位命令</t>
         </is>
       </c>
-      <c r="F17" s="10" t="str"/>
+      <c r="F17" s="16" t="str"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>M4121</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>軸1_X橫移_檢查位/等待位命令</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Axis1 X traverse 檢查位/等待位 command</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>定位命令</t>
         </is>
       </c>
-      <c r="F18" s="10" t="str"/>
+      <c r="F18" s="19" t="str"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>M4122</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移_上機盒位命令</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>Axis1 X traverse 上機盒位 command</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>軸1_X橫移</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>定位命令</t>
         </is>
       </c>
-      <c r="F19" s="10" t="str"/>
+      <c r="F19" s="16" t="str"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>M4150</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>軸1_X橫移_儲存盒位到位</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Axis1 X traverse 儲存盒位 complete</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>軸1_X橫移</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>定位完成</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>完成條件統一: Ready + Busy OFF + InPosition + Alarm OFF + 誤差&lt;=Tolerance</t>
-        </is>
-      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>軸1_儲存盒位到位</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Axis1 storage position complete</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>到位</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>M4127 OFF + InPosition + Error&lt;=D4100。</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>M4151</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>軸1_X橫移_檢查位/等待位到位</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Axis1 X traverse 檢查位/等待位 complete</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>軸1_X橫移</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>定位完成</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>完成條件統一: Ready + Busy OFF + InPosition + Alarm OFF + 誤差&lt;=Tolerance</t>
-        </is>
-      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>軸1_檢查位到位</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Axis1 inspection position complete</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>到位</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>M4127 OFF + InPosition + Error&lt;=D4100。</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>M4152</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>軸1_X橫移_上機盒位到位</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Axis1 X traverse 上機盒位 complete</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>軸1_X橫移</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>定位完成</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>完成條件統一: Ready + Busy OFF + InPosition + Alarm OFF + 誤差&lt;=Tolerance</t>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>軸1_上機盒位到位</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Axis1 load position complete</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>到位</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>M4127 OFF + InPosition + Error&lt;=D4100。</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>M4117</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>軸1_X橫移_Ready</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Axis1 X traverse ready</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>安全OK + MC送電 + Servo ON + Alarm OFF + 軸卡Ready。</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>Coding時作自動/手動允許。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>M4118</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>軸1_X橫移_Alarm</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Axis1 X traverse alarm</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>軸卡Alarm/伺服Alarm/Timeout/極限異常總成。</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>Alarm Detail需顯示來源。</t>
         </is>
       </c>
     </row>
@@ -12025,32 +14285,32 @@
       <c r="F23" s="16" t="str"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>M4327</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>軸2_X升降_真空確認位命令</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Axis2 X lift 真空確認位 command</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>軸2_X升降</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>定位命令</t>
         </is>
       </c>
-      <c r="F24" s="16" t="str"/>
+      <c r="F24" s="19" t="str"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -12299,7 +14559,7 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>取片後上升約10mm真空確認，若各位置高度不同需拆D4424或新增命令。</t>
+          <t>取片後上升約10mm真空確認。</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -12444,12 +14704,12 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>軸2_Ready</t>
+          <t>軸2_X升降_Ready</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>Axis2 ready</t>
+          <t>Axis2 X lift ready</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -12459,10 +14719,14 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>Servo Ready + Alarm OFF + Safety OK。</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr"/>
+          <t>安全OK + MC送電 + Servo ON + Brake release condition + Alarm OFF + 軸卡Ready。</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>垂直軸需含煞車互鎖。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -12472,12 +14736,12 @@
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>軸2_Alarm</t>
+          <t>軸2_X升降_Alarm</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>Axis2 alarm</t>
+          <t>Axis2 X lift alarm</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
@@ -12487,10 +14751,14 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>軸卡/伺服/流程異常總成。</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr"/>
+          <t>軸卡Alarm/伺服Alarm/Timeout/極限/煞車異常總成。</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>Alarm Detail需顯示來源。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -12515,7 +14783,7 @@
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>HMI M6014驅動。</t>
+          <t>HMI M6014驅動，需M6200允許。</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr"/>
@@ -12543,7 +14811,7 @@
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>HMI M6013驅動。</t>
+          <t>HMI M6013驅動，需M6200允許。</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr"/>
@@ -13898,7 +16166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15062,64 +17330,64 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>D6402</t>
         </is>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>Barcode NG原因碼</t>
         </is>
       </c>
-      <c r="C40" s="16" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>Barcode NG reason code</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="18" t="inlineStr">
         <is>
           <t>Barcode</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E40" s="18" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F40" s="18" t="inlineStr">
         <is>
           <t>比對失敗/無讀取/通訊逾時等。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>D6404</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>Barcode NG原因碼</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Barcode NG reason code</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>Barcode結果</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E41" s="18" t="inlineStr">
         <is>
           <t>1無讀碼 2格式錯 3字串不符 4Timeout 5人工失敗</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr"/>
+      <c r="F41" s="18" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -15850,6 +18118,326 @@
       <c r="F64" s="16" t="inlineStr">
         <is>
           <t>ABS(目前位置-D4424)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>D6004</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>目前警報碼</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>Current alarm code</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>HMI Alarm Detail顯示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t>D6006</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>目前異常Step</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>Current fault step</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>異常發生時保存S/D6401。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
+          <t>D6008</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>目前異常軸號</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>Current fault axis</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>0共用、1軸1、2軸2、3軸3、4軸4。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t>D6010</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>目前異常料態</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>Current fault material state</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>保存D6100。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>D6020</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Move Timeout設定</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>Move timeout setting</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>所有定位逾時基準，可依軸另外覆寫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t>D6022</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Grip Timeout設定</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>Grip timeout setting</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>夾爪開/關到位逾時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>D6024</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>Vacuum Build Timeout設定</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>Vacuum build timeout setting</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>真空建立逾時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t>D6026</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Vacuum Release Timeout設定</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>Vacuum release timeout setting</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>破真空逾時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
+        <is>
+          <t>D6028</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Z Handshake Timeout設定</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>Z handshake timeout setting</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>Timeout</t>
+        </is>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>等待M6102/M6103逾時。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>D6101</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>人工料態設定值</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>Manual material state set value</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>需Engineer權限、M6030 Apply、二次確認，Auto Busy禁止。</t>
         </is>
       </c>
     </row>
